--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_13-03-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_13-03-2026.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="373">
   <si>
     <t>SKU</t>
   </si>
@@ -241,7 +241,7 @@
     <t>£10.25</t>
   </si>
   <si>
-    <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
+    <t>£12.05</t>
   </si>
   <si>
     <t>£14.87</t>
@@ -319,22 +319,7 @@
     <t>£1,275.65</t>
   </si>
   <si>
-    <t>£12.05</t>
-  </si>
-  <si>
-    <t>Error: 503 Server Error: Service Unavailable for url: https://build4less.co.uk/products/100mm-celotex-ga4100-2-4m-x-1-2m</t>
-  </si>
-  <si>
-    <t>Error: 503 Server Error: Service Unavailable for url: https://build4less.co.uk/products/110mm-celotex-xr4110-2-4m-x-1-2m</t>
-  </si>
-  <si>
-    <t>Error: 503 Server Error: Service Unavailable for url: https://www.building-supplies-online.co.uk/products/celotex-ga4000-insulation-board-1200-x-2400mm?variant=55597620003200</t>
-  </si>
-  <si>
-    <t>Error: 503 Server Error: Service Unavailable for url: https://www.building-supplies-online.co.uk/products/celotex-ga4000-insulation-board-1200-x-2400mm?variant=55597620068736</t>
-  </si>
-  <si>
-    <t>Error: 503 Server Error: Service Unavailable for url: https://www.building-supplies-online.co.uk/products/celotex-xr4000-insulation-pitched-roof-board-1200-x-2400mm?variant=55597620494720</t>
+    <t>Error: 503 Server Error: Service Unavailable for url: https://build4less.co.uk/products/50mm-celotex-ga4050-2-4m-x-1-2m</t>
   </si>
   <si>
     <t>N/L</t>
@@ -529,76 +514,76 @@
     <t>£1276.0</t>
   </si>
   <si>
-    <t>£13.4</t>
-  </si>
-  <si>
-    <t>£15.4</t>
-  </si>
-  <si>
-    <t>£19.75</t>
-  </si>
-  <si>
-    <t>£20.1</t>
-  </si>
-  <si>
-    <t>£25.75</t>
-  </si>
-  <si>
-    <t>£27.78</t>
-  </si>
-  <si>
-    <t>£28.2</t>
-  </si>
-  <si>
-    <t>£35.2</t>
-  </si>
-  <si>
-    <t>£50.15</t>
-  </si>
-  <si>
-    <t>£42.1</t>
-  </si>
-  <si>
-    <t>£56.09</t>
-  </si>
-  <si>
-    <t>£56.75</t>
+    <t>£11.17</t>
+  </si>
+  <si>
+    <t>£12.83</t>
+  </si>
+  <si>
+    <t>£16.46</t>
+  </si>
+  <si>
+    <t>£16.75</t>
+  </si>
+  <si>
+    <t>£21.46</t>
   </si>
   <si>
     <t>POA</t>
   </si>
   <si>
-    <t>£1029.48</t>
-  </si>
-  <si>
-    <t>£1235.4</t>
-  </si>
-  <si>
-    <t>£44.87</t>
-  </si>
-  <si>
-    <t>£59.39</t>
-  </si>
-  <si>
-    <t>£65.99</t>
-  </si>
-  <si>
-    <t>£94.27</t>
-  </si>
-  <si>
-    <t>£102.56</t>
-  </si>
-  <si>
-    <t>£98.28</t>
-  </si>
-  <si>
-    <t>£1406.4</t>
-  </si>
-  <si>
-    <t>£1688.8</t>
-  </si>
-  <si>
-    <t>£1604.48</t>
+    <t>£23.5</t>
+  </si>
+  <si>
+    <t>£26.79</t>
+  </si>
+  <si>
+    <t>£29.33</t>
+  </si>
+  <si>
+    <t>£27.29</t>
+  </si>
+  <si>
+    <t>£41.79</t>
+  </si>
+  <si>
+    <t>£35.08</t>
+  </si>
+  <si>
+    <t>£47.29</t>
+  </si>
+  <si>
+    <t>£43.58</t>
+  </si>
+  <si>
+    <t>£857.9</t>
+  </si>
+  <si>
+    <t>£1029.5</t>
+  </si>
+  <si>
+    <t>£37.39</t>
+  </si>
+  <si>
+    <t>£49.49</t>
+  </si>
+  <si>
+    <t>£54.99</t>
+  </si>
+  <si>
+    <t>£78.56</t>
+  </si>
+  <si>
+    <t>£85.47</t>
+  </si>
+  <si>
+    <t>£81.9</t>
+  </si>
+  <si>
+    <t>£1172.0</t>
+  </si>
+  <si>
+    <t>£1407.33</t>
   </si>
   <si>
     <t>£13.29</t>
@@ -754,9 +739,6 @@
     <t>Price Not Found</t>
   </si>
   <si>
-    <t>Error: 503 Server Error: Service Unavailable for url: https://www.planetinsulation.co.uk/products/celotex-pir-tb-ga-xr?variant=42844828565741</t>
-  </si>
-  <si>
     <t>£11.28</t>
   </si>
   <si>
@@ -844,18 +826,12 @@
     <t>£23.87</t>
   </si>
   <si>
-    <t>£27.67</t>
-  </si>
-  <si>
     <t>£29.74</t>
   </si>
   <si>
     <t>£32.42</t>
   </si>
   <si>
-    <t>£39.12</t>
-  </si>
-  <si>
     <t>£46.64</t>
   </si>
   <si>
@@ -880,9 +856,15 @@
     <t>£86.21</t>
   </si>
   <si>
+    <t>£89.87</t>
+  </si>
+  <si>
     <t>£51.20</t>
   </si>
   <si>
+    <t>£59.20</t>
+  </si>
+  <si>
     <t>£79.58</t>
   </si>
   <si>
@@ -1087,9 +1069,6 @@
     <t>£1377.12</t>
   </si>
   <si>
-    <t>£11.17</t>
-  </si>
-  <si>
     <t>£16.66</t>
   </si>
   <si>
@@ -1109,9 +1088,6 @@
   </si>
   <si>
     <t>£29.78</t>
-  </si>
-  <si>
-    <t>£29.33</t>
   </si>
   <si>
     <t>£36.01</t>
@@ -1590,43 +1566,43 @@
         <v>74</v>
       </c>
       <c r="F2" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="G2" t="s">
         <v>74</v>
       </c>
       <c r="H2" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="I2" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="J2" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="K2" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="L2" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="M2" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="N2" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="O2" t="s">
         <v>74</v>
       </c>
       <c r="P2" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="Q2" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="R2" t="s">
-        <v>357</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1640,49 +1616,49 @@
         <v>75</v>
       </c>
       <c r="D3" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="E3" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="F3" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="G3" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="H3" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="I3" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="J3" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="K3" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="L3" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="M3" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="N3" t="s">
-        <v>276</v>
+        <v>171</v>
       </c>
       <c r="O3" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="P3" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="Q3" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="R3" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1702,43 +1678,43 @@
         <v>76</v>
       </c>
       <c r="F4" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="G4" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="H4" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="I4" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="J4" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="K4" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="L4" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="M4" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="N4" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="O4" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="P4" t="s">
         <v>76</v>
       </c>
       <c r="Q4" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="R4" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1752,49 +1728,49 @@
         <v>77</v>
       </c>
       <c r="D5" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="E5" t="s">
         <v>77</v>
       </c>
       <c r="F5" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="G5" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="H5" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="I5" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="J5" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="K5" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="L5" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="M5" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="N5" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="O5" t="s">
         <v>77</v>
       </c>
       <c r="P5" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="Q5" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="R5" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1814,43 +1790,43 @@
         <v>78</v>
       </c>
       <c r="F6" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="G6" t="s">
         <v>78</v>
       </c>
       <c r="H6" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="I6" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="J6" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="K6" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="L6" t="s">
+        <v>240</v>
+      </c>
+      <c r="M6" t="s">
         <v>245</v>
       </c>
-      <c r="M6" t="s">
-        <v>251</v>
-      </c>
       <c r="N6" t="s">
-        <v>279</v>
+        <v>171</v>
       </c>
       <c r="O6" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="P6" t="s">
         <v>78</v>
       </c>
       <c r="Q6" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="R6" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1870,43 +1846,43 @@
         <v>79</v>
       </c>
       <c r="F7" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="G7" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="H7" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="I7" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="J7" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="K7" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="L7" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="M7" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="N7" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="O7" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="P7" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="Q7" t="s">
         <v>79</v>
       </c>
       <c r="R7" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1926,43 +1902,43 @@
         <v>79</v>
       </c>
       <c r="F8" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="G8" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="H8" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="I8" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="J8" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="K8" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="L8" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="M8" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="N8" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="O8" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="P8" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="Q8" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="R8" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1979,46 +1955,46 @@
         <v>80</v>
       </c>
       <c r="E9" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="F9" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="G9" t="s">
         <v>80</v>
       </c>
       <c r="H9" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="I9" t="s">
-        <v>137</v>
+        <v>173</v>
       </c>
       <c r="J9" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="K9" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="L9" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="M9" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="N9" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="O9" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="P9" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="Q9" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="R9" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -2038,43 +2014,43 @@
         <v>81</v>
       </c>
       <c r="F10" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="G10" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="H10" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="I10" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="J10" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="K10" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="L10" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="M10" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="N10" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="O10" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="P10" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="Q10" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="R10" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -2088,49 +2064,49 @@
         <v>82</v>
       </c>
       <c r="D11" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="E11" t="s">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="F11" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="G11" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="H11" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="I11" t="s">
-        <v>84</v>
+        <v>175</v>
       </c>
       <c r="J11" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="K11" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="L11" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="M11" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="N11" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="O11" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="P11" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="Q11" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="R11" t="s">
-        <v>365</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -2144,49 +2120,49 @@
         <v>83</v>
       </c>
       <c r="D12" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="E12" t="s">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="F12" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="G12" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="H12" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="I12" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="J12" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="K12" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="L12" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="M12" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="N12" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="O12" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="P12" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="Q12" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="R12" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -2206,43 +2182,43 @@
         <v>84</v>
       </c>
       <c r="F13" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="G13" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="H13" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="I13" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="J13" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="K13" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="L13" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="M13" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="N13" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="O13" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="P13" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="Q13" t="s">
         <v>84</v>
       </c>
       <c r="R13" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2262,43 +2238,43 @@
         <v>85</v>
       </c>
       <c r="F14" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="G14" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="H14" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="I14" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="J14" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="K14" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="L14" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="M14" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="N14" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="O14" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="P14" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="Q14" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="R14" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2315,46 +2291,46 @@
         <v>86</v>
       </c>
       <c r="E15" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="F15" t="s">
         <v>97</v>
       </c>
       <c r="G15" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="H15" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="I15" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="J15" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="K15" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="L15" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="M15" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="N15" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="O15" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="P15" t="s">
         <v>86</v>
       </c>
       <c r="Q15" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="R15" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2374,31 +2350,31 @@
         <v>87</v>
       </c>
       <c r="F16" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="G16" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="H16" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="I16" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="J16" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="K16" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="L16" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="M16" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="N16" t="s">
-        <v>183</v>
+        <v>280</v>
       </c>
       <c r="O16" t="s">
         <v>87</v>
@@ -2407,10 +2383,10 @@
         <v>87</v>
       </c>
       <c r="Q16" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="R16" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2430,43 +2406,43 @@
         <v>88</v>
       </c>
       <c r="F17" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="G17" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="H17" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="I17" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="J17" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="K17" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="L17" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="M17" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="N17" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="O17" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="P17" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="Q17" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="R17" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2486,43 +2462,43 @@
         <v>89</v>
       </c>
       <c r="F18" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G18" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="H18" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="I18" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="J18" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="K18" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="L18" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="M18" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="N18" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="O18" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="P18" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="Q18" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="R18" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2542,43 +2518,43 @@
         <v>90</v>
       </c>
       <c r="F19" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="G19" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="H19" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="I19" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="J19" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="K19" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="L19" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="M19" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="N19" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="O19" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="P19" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="Q19" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="R19" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2598,43 +2574,43 @@
         <v>91</v>
       </c>
       <c r="F20" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="G20" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="H20" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="I20" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="J20" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="K20" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="L20" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="M20" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="N20" t="s">
-        <v>183</v>
+        <v>282</v>
       </c>
       <c r="O20" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="P20" t="s">
         <v>91</v>
       </c>
       <c r="Q20" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="R20" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2654,43 +2630,43 @@
         <v>92</v>
       </c>
       <c r="F21" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="G21" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="H21" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="I21" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="J21" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="K21" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="L21" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="M21" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="N21" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="O21" t="s">
         <v>92</v>
       </c>
       <c r="P21" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="Q21" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="R21" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -2710,43 +2686,43 @@
         <v>93</v>
       </c>
       <c r="F22" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="G22" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="H22" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="I22" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="J22" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="K22" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="L22" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="M22" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="N22" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="O22" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="P22" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="Q22" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="R22" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -2766,43 +2742,43 @@
         <v>94</v>
       </c>
       <c r="F23" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="G23" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="H23" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="I23" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J23" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="K23" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="L23" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="M23" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="N23" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="O23" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="P23" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="Q23" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="R23" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -2822,43 +2798,43 @@
         <v>95</v>
       </c>
       <c r="F24" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="G24" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="H24" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="I24" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="J24" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="K24" t="s">
+        <v>235</v>
+      </c>
+      <c r="L24" t="s">
         <v>240</v>
       </c>
-      <c r="L24" t="s">
-        <v>245</v>
-      </c>
       <c r="M24" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="N24" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="O24" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="P24" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="Q24" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="R24" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
     </row>
     <row r="25" spans="1:18">
@@ -2878,43 +2854,43 @@
         <v>96</v>
       </c>
       <c r="F25" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="G25" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="H25" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="I25" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="J25" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="K25" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="L25" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="M25" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="N25" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="O25" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="P25" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="Q25" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="R25" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="26" spans="1:18">
@@ -2934,43 +2910,43 @@
         <v>97</v>
       </c>
       <c r="F26" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="G26" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="H26" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="I26" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="J26" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="K26" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="L26" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="M26" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="N26" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="O26" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="P26" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="Q26" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="R26" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
     </row>
     <row r="27" spans="1:18">
@@ -2990,43 +2966,43 @@
         <v>98</v>
       </c>
       <c r="F27" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="G27" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="H27" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="I27" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="J27" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="K27" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="L27" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="M27" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="N27" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="O27" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="P27" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="Q27" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="R27" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
     </row>
     <row r="28" spans="1:18">
@@ -3046,43 +3022,43 @@
         <v>99</v>
       </c>
       <c r="F28" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="G28" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="H28" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="I28" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="J28" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="K28" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="L28" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="M28" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="N28" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="O28" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="P28" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="Q28" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="R28" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
     </row>
     <row r="29" spans="1:18">
@@ -3102,43 +3078,43 @@
         <v>100</v>
       </c>
       <c r="F29" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="G29" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="H29" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="I29" t="s">
-        <v>194</v>
+        <v>171</v>
       </c>
       <c r="J29" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="K29" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="L29" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="M29" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="N29" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="O29" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="P29" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="Q29" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="R29" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
     </row>
   </sheetData>

--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_13-03-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_13-03-2026.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="360">
   <si>
     <t>SKU</t>
   </si>
@@ -238,88 +238,100 @@
     <t>Celotex Thermaclass Cavity Wall 21 140mm x 1.19m x 0.45m (64 Sh / 34.27m2)</t>
   </si>
   <si>
+    <t>Error: HTTPSConnectionPool(host='insulation4less.co.uk', port=443): Max retries exceeded with url: /products/25mm-celotex-tb3025-2-4m-x-1-2m (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x000001DFEDBE4AD0&gt;, 'Connection to insulation4less.co.uk timed out. (connect timeout=30)'))</t>
+  </si>
+  <si>
+    <t>£12.05</t>
+  </si>
+  <si>
+    <t>£14.87</t>
+  </si>
+  <si>
+    <t>£15.84</t>
+  </si>
+  <si>
+    <t>£19.65</t>
+  </si>
+  <si>
+    <t>£22.00</t>
+  </si>
+  <si>
+    <t>£25.05</t>
+  </si>
+  <si>
+    <t>£27.40</t>
+  </si>
+  <si>
+    <t>£26.67</t>
+  </si>
+  <si>
+    <t>£32.40</t>
+  </si>
+  <si>
+    <t>£32.75</t>
+  </si>
+  <si>
+    <t>£39.40</t>
+  </si>
+  <si>
+    <t>£39.99</t>
+  </si>
+  <si>
+    <t>£40.35</t>
+  </si>
+  <si>
+    <t>£745.00</t>
+  </si>
+  <si>
+    <t>£935.00</t>
+  </si>
+  <si>
+    <t>£28.00</t>
+  </si>
+  <si>
+    <t>£34.43</t>
+  </si>
+  <si>
+    <t>£36.99</t>
+  </si>
+  <si>
+    <t>£42.10</t>
+  </si>
+  <si>
+    <t>£44.80</t>
+  </si>
+  <si>
+    <t>£43.65</t>
+  </si>
+  <si>
+    <t>£925.79</t>
+  </si>
+  <si>
+    <t>£42.95</t>
+  </si>
+  <si>
+    <t>£1,195.00</t>
+  </si>
+  <si>
+    <t>£1,319.33</t>
+  </si>
+  <si>
+    <t>£1,275.65</t>
+  </si>
+  <si>
+    <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/25mm-celotex-tb3025-2-4m-x-1-2m (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x000001DFEDC69090&gt;, 'Connection to build4less.co.uk timed out. (connect timeout=30)'))</t>
+  </si>
+  <si>
+    <t>Error: 503 Server Error: Service Unavailable for url: https://build4less.co.uk/products/40mm-celotex-tb3040-2-4m-x-1-2m</t>
+  </si>
+  <si>
+    <t>Error: 503 Server Error: Service Unavailable for url: https://build4less.co.uk/products/50mm-celotex-ga4050-2-4m-x-1-2m</t>
+  </si>
+  <si>
     <t>£10.25</t>
   </si>
   <si>
-    <t>£12.05</t>
-  </si>
-  <si>
-    <t>£14.87</t>
-  </si>
-  <si>
-    <t>£15.84</t>
-  </si>
-  <si>
-    <t>£19.65</t>
-  </si>
-  <si>
-    <t>£22.00</t>
-  </si>
-  <si>
-    <t>£25.05</t>
-  </si>
-  <si>
-    <t>£27.40</t>
-  </si>
-  <si>
-    <t>£26.67</t>
-  </si>
-  <si>
-    <t>£32.40</t>
-  </si>
-  <si>
-    <t>£32.75</t>
-  </si>
-  <si>
-    <t>£39.40</t>
-  </si>
-  <si>
-    <t>£39.99</t>
-  </si>
-  <si>
-    <t>£40.35</t>
-  </si>
-  <si>
-    <t>£745.00</t>
-  </si>
-  <si>
-    <t>£935.00</t>
-  </si>
-  <si>
-    <t>£28.00</t>
-  </si>
-  <si>
-    <t>£34.43</t>
-  </si>
-  <si>
-    <t>£36.99</t>
-  </si>
-  <si>
-    <t>£42.10</t>
-  </si>
-  <si>
-    <t>£44.80</t>
-  </si>
-  <si>
-    <t>£43.65</t>
-  </si>
-  <si>
-    <t>£925.79</t>
-  </si>
-  <si>
-    <t>£42.95</t>
-  </si>
-  <si>
-    <t>£1,195.00</t>
-  </si>
-  <si>
-    <t>£1,319.33</t>
-  </si>
-  <si>
-    <t>£1,275.65</t>
-  </si>
-  <si>
-    <t>Error: 503 Server Error: Service Unavailable for url: https://build4less.co.uk/products/50mm-celotex-ga4050-2-4m-x-1-2m</t>
+    <t>Error: 503 Server Error: Service Unavailable for url: https://www.building-supplies-online.co.uk/products/celotex-ga4000-insulation-board-1200-x-2400mm?variant=55597619872128</t>
   </si>
   <si>
     <t>N/L</t>
@@ -397,6 +409,9 @@
     <t>£15.82</t>
   </si>
   <si>
+    <t>Error: 503 Server Error: Service Unavailable for url: https://www.insulationuk.co.uk/products/60mm-celotex-ga4060-pir-insulation-board-2400mm-x-1200mm-x-60mm</t>
+  </si>
+  <si>
     <t>£21.89</t>
   </si>
   <si>
@@ -514,580 +529,526 @@
     <t>£1276.0</t>
   </si>
   <si>
-    <t>£11.17</t>
-  </si>
-  <si>
-    <t>£12.83</t>
-  </si>
-  <si>
-    <t>£16.46</t>
-  </si>
-  <si>
-    <t>£16.75</t>
-  </si>
-  <si>
-    <t>£21.46</t>
+    <t>£0.0</t>
   </si>
   <si>
     <t>POA</t>
   </si>
   <si>
-    <t>£23.5</t>
-  </si>
-  <si>
-    <t>£26.79</t>
+    <t>£39113.07</t>
+  </si>
+  <si>
+    <t>£13.29</t>
+  </si>
+  <si>
+    <t>£15.98</t>
+  </si>
+  <si>
+    <t>£19.83</t>
+  </si>
+  <si>
+    <t>£21.35</t>
+  </si>
+  <si>
+    <t>£25.28</t>
+  </si>
+  <si>
+    <t>£28.92</t>
+  </si>
+  <si>
+    <t>£27.86</t>
+  </si>
+  <si>
+    <t>£31.31</t>
+  </si>
+  <si>
+    <t>£35.78</t>
+  </si>
+  <si>
+    <t>£34.88</t>
+  </si>
+  <si>
+    <t>£43.29</t>
+  </si>
+  <si>
+    <t>£42.93</t>
+  </si>
+  <si>
+    <t>£51.18</t>
+  </si>
+  <si>
+    <t>£54.76</t>
+  </si>
+  <si>
+    <t>£51.67</t>
+  </si>
+  <si>
+    <t>£1,125.19</t>
+  </si>
+  <si>
+    <t>£38.02</t>
+  </si>
+  <si>
+    <t>£45.21</t>
+  </si>
+  <si>
+    <t>£53.64</t>
+  </si>
+  <si>
+    <t>£58.99</t>
+  </si>
+  <si>
+    <t>£63.95</t>
+  </si>
+  <si>
+    <t>£63.02</t>
+  </si>
+  <si>
+    <t>£1032.8</t>
+  </si>
+  <si>
+    <t>£60.74</t>
+  </si>
+  <si>
+    <t>£10.74</t>
+  </si>
+  <si>
+    <t>£13.07</t>
+  </si>
+  <si>
+    <t>£15.87</t>
+  </si>
+  <si>
+    <t>£16.96</t>
+  </si>
+  <si>
+    <t>£21.12</t>
+  </si>
+  <si>
+    <t>£23.8</t>
+  </si>
+  <si>
+    <t>£23.05</t>
+  </si>
+  <si>
+    <t>£26.23</t>
+  </si>
+  <si>
+    <t>£28.99</t>
+  </si>
+  <si>
+    <t>£35.09</t>
+  </si>
+  <si>
+    <t>£36.27</t>
+  </si>
+  <si>
+    <t>£41.12</t>
+  </si>
+  <si>
+    <t>£44.39</t>
+  </si>
+  <si>
+    <t>£43.55</t>
+  </si>
+  <si>
+    <t>£697.98</t>
+  </si>
+  <si>
+    <t>£939.1</t>
+  </si>
+  <si>
+    <t>£40.65</t>
+  </si>
+  <si>
+    <t>£48.65</t>
+  </si>
+  <si>
+    <t>£57.54</t>
+  </si>
+  <si>
+    <t>£61.03</t>
+  </si>
+  <si>
+    <t>£45.36</t>
+  </si>
+  <si>
+    <t>£43.3</t>
+  </si>
+  <si>
+    <t>£44.58</t>
+  </si>
+  <si>
+    <t>£1163.76</t>
+  </si>
+  <si>
+    <t>£1238.58</t>
+  </si>
+  <si>
+    <t>£1206.21</t>
+  </si>
+  <si>
+    <t>Price Not Found</t>
+  </si>
+  <si>
+    <t>£11.28</t>
+  </si>
+  <si>
+    <t>£13.05</t>
+  </si>
+  <si>
+    <t>£16.05</t>
+  </si>
+  <si>
+    <t>£17.83</t>
+  </si>
+  <si>
+    <t>£21.36</t>
+  </si>
+  <si>
+    <t>£23.13</t>
+  </si>
+  <si>
+    <t>£23.53</t>
+  </si>
+  <si>
+    <t>£25.89</t>
+  </si>
+  <si>
+    <t>£33.90</t>
+  </si>
+  <si>
+    <t>£29.72</t>
+  </si>
+  <si>
+    <t>£56.06</t>
+  </si>
+  <si>
+    <t>£35.79</t>
+  </si>
+  <si>
+    <t>£40.85</t>
+  </si>
+  <si>
+    <t>£44.28</t>
+  </si>
+  <si>
+    <t>£43.42</t>
+  </si>
+  <si>
+    <t>£1055.68</t>
+  </si>
+  <si>
+    <t>£1280.46</t>
+  </si>
+  <si>
+    <t>£53.06</t>
+  </si>
+  <si>
+    <t>£64.38</t>
+  </si>
+  <si>
+    <t>£72.69</t>
+  </si>
+  <si>
+    <t>£75.76</t>
+  </si>
+  <si>
+    <t>£72.03</t>
+  </si>
+  <si>
+    <t>£69.95</t>
+  </si>
+  <si>
+    <t>£1582.88</t>
+  </si>
+  <si>
+    <t>£68.22</t>
+  </si>
+  <si>
+    <t>£1747.68</t>
+  </si>
+  <si>
+    <t>£1870.08</t>
+  </si>
+  <si>
+    <t>£1984.64</t>
+  </si>
+  <si>
+    <t>£27.67</t>
+  </si>
+  <si>
+    <t>£29.74</t>
+  </si>
+  <si>
+    <t>£32.42</t>
+  </si>
+  <si>
+    <t>£39.12</t>
+  </si>
+  <si>
+    <t>£46.64</t>
+  </si>
+  <si>
+    <t>£46.55</t>
+  </si>
+  <si>
+    <t>£51.7</t>
+  </si>
+  <si>
+    <t>£57.31</t>
+  </si>
+  <si>
+    <t>£49.55</t>
+  </si>
+  <si>
+    <t>£74.18</t>
+  </si>
+  <si>
+    <t>£81.55</t>
+  </si>
+  <si>
+    <t>£86.21</t>
+  </si>
+  <si>
+    <t>£89.87</t>
+  </si>
+  <si>
+    <t>£51.2</t>
+  </si>
+  <si>
+    <t>£59.2</t>
+  </si>
+  <si>
+    <t>£79.58</t>
+  </si>
+  <si>
+    <t>£70.18</t>
+  </si>
+  <si>
+    <t>£12.07</t>
+  </si>
+  <si>
+    <t>£15.24</t>
+  </si>
+  <si>
+    <t>£19.67</t>
+  </si>
+  <si>
+    <t>£22.05</t>
+  </si>
+  <si>
+    <t>£22.09</t>
+  </si>
+  <si>
+    <t>£25.07</t>
+  </si>
+  <si>
+    <t>£27.59</t>
+  </si>
+  <si>
+    <t>£27.15</t>
+  </si>
+  <si>
+    <t>£32.99</t>
+  </si>
+  <si>
+    <t>£33.38</t>
+  </si>
+  <si>
+    <t>£39.79</t>
+  </si>
+  <si>
+    <t>£41.99</t>
+  </si>
+  <si>
+    <t>£779.88</t>
+  </si>
+  <si>
+    <t>£1019.88</t>
+  </si>
+  <si>
+    <t>£28.12</t>
+  </si>
+  <si>
+    <t>£34.75</t>
+  </si>
+  <si>
+    <t>£42.40</t>
+  </si>
+  <si>
+    <t>£45.74</t>
+  </si>
+  <si>
+    <t>£43.75</t>
+  </si>
+  <si>
+    <t>£924.00</t>
+  </si>
+  <si>
+    <t>£43.69</t>
+  </si>
+  <si>
+    <t>£1199.84</t>
+  </si>
+  <si>
+    <t>£1336.0</t>
+  </si>
+  <si>
+    <t>£1359.84</t>
+  </si>
+  <si>
+    <t>£10.3</t>
+  </si>
+  <si>
+    <t>£12.09</t>
+  </si>
+  <si>
+    <t>£15.86</t>
+  </si>
+  <si>
+    <t>£22.0</t>
+  </si>
+  <si>
+    <t>£27.4</t>
+  </si>
+  <si>
+    <t>£26.8</t>
+  </si>
+  <si>
+    <t>£32.98</t>
+  </si>
+  <si>
+    <t>£39.4</t>
+  </si>
+  <si>
+    <t>£804.0</t>
+  </si>
+  <si>
+    <t>£945.0</t>
+  </si>
+  <si>
+    <t>£28.03</t>
+  </si>
+  <si>
+    <t>£37.07</t>
+  </si>
+  <si>
+    <t>£42.15</t>
+  </si>
+  <si>
+    <t>£55.13</t>
+  </si>
+  <si>
+    <t>£53.4</t>
+  </si>
+  <si>
+    <t>£51.65</t>
+  </si>
+  <si>
+    <t>£1248.0</t>
+  </si>
+  <si>
+    <t>£1328.0</t>
+  </si>
+  <si>
+    <t>£1280.0</t>
+  </si>
+  <si>
+    <t>£10.15</t>
+  </si>
+  <si>
+    <t>£12.55</t>
+  </si>
+  <si>
+    <t>£14.83</t>
+  </si>
+  <si>
+    <t>£15.77</t>
+  </si>
+  <si>
+    <t>£19.71</t>
+  </si>
+  <si>
+    <t>£22.11</t>
+  </si>
+  <si>
+    <t>£25.12</t>
+  </si>
+  <si>
+    <t>£27.44</t>
+  </si>
+  <si>
+    <t>£26.49</t>
+  </si>
+  <si>
+    <t>£38.80</t>
+  </si>
+  <si>
+    <t>£38.92</t>
+  </si>
+  <si>
+    <t>£39.81</t>
+  </si>
+  <si>
+    <t>£9008.4</t>
+  </si>
+  <si>
+    <t>Error: could not convert string to float: '1,035.75'</t>
+  </si>
+  <si>
+    <t>£28.33</t>
+  </si>
+  <si>
+    <t>£32.69</t>
+  </si>
+  <si>
+    <t>£35.92</t>
+  </si>
+  <si>
+    <t>£40.99</t>
+  </si>
+  <si>
+    <t>£44.16</t>
+  </si>
+  <si>
+    <t>£43.59</t>
+  </si>
+  <si>
+    <t>£43.14</t>
+  </si>
+  <si>
+    <t>£1224.64</t>
+  </si>
+  <si>
+    <t>£1377.12</t>
+  </si>
+  <si>
+    <t>Error: 503 Server Error: Service Unavailable for url: https://diybuildingsupplies.co.uk/products/celotex-tb4025-high-performance-pir-insulation-2400mm-x-1200mm-x-25mm</t>
+  </si>
+  <si>
+    <t>£16.66</t>
+  </si>
+  <si>
+    <t>£17.30</t>
+  </si>
+  <si>
+    <t>£21.13</t>
+  </si>
+  <si>
+    <t>£24.35</t>
+  </si>
+  <si>
+    <t>£23.47</t>
+  </si>
+  <si>
+    <t>£26.39</t>
+  </si>
+  <si>
+    <t>£29.78</t>
   </si>
   <si>
     <t>£29.33</t>
-  </si>
-  <si>
-    <t>£27.29</t>
-  </si>
-  <si>
-    <t>£41.79</t>
-  </si>
-  <si>
-    <t>£35.08</t>
-  </si>
-  <si>
-    <t>£47.29</t>
-  </si>
-  <si>
-    <t>£43.58</t>
-  </si>
-  <si>
-    <t>£857.9</t>
-  </si>
-  <si>
-    <t>£1029.5</t>
-  </si>
-  <si>
-    <t>£37.39</t>
-  </si>
-  <si>
-    <t>£49.49</t>
-  </si>
-  <si>
-    <t>£54.99</t>
-  </si>
-  <si>
-    <t>£78.56</t>
-  </si>
-  <si>
-    <t>£85.47</t>
-  </si>
-  <si>
-    <t>£81.9</t>
-  </si>
-  <si>
-    <t>£1172.0</t>
-  </si>
-  <si>
-    <t>£1407.33</t>
-  </si>
-  <si>
-    <t>£13.29</t>
-  </si>
-  <si>
-    <t>£15.98</t>
-  </si>
-  <si>
-    <t>£19.83</t>
-  </si>
-  <si>
-    <t>£21.35</t>
-  </si>
-  <si>
-    <t>£25.28</t>
-  </si>
-  <si>
-    <t>£28.92</t>
-  </si>
-  <si>
-    <t>£27.86</t>
-  </si>
-  <si>
-    <t>£31.31</t>
-  </si>
-  <si>
-    <t>£35.78</t>
-  </si>
-  <si>
-    <t>£34.88</t>
-  </si>
-  <si>
-    <t>£43.29</t>
-  </si>
-  <si>
-    <t>£42.93</t>
-  </si>
-  <si>
-    <t>£51.18</t>
-  </si>
-  <si>
-    <t>£54.76</t>
-  </si>
-  <si>
-    <t>£51.67</t>
-  </si>
-  <si>
-    <t>£1,125.19</t>
-  </si>
-  <si>
-    <t>£38.02</t>
-  </si>
-  <si>
-    <t>£45.21</t>
-  </si>
-  <si>
-    <t>£53.64</t>
-  </si>
-  <si>
-    <t>£58.99</t>
-  </si>
-  <si>
-    <t>£63.95</t>
-  </si>
-  <si>
-    <t>£63.02</t>
-  </si>
-  <si>
-    <t>£1032.8</t>
-  </si>
-  <si>
-    <t>£60.74</t>
-  </si>
-  <si>
-    <t>£10.74</t>
-  </si>
-  <si>
-    <t>£13.07</t>
-  </si>
-  <si>
-    <t>£15.87</t>
-  </si>
-  <si>
-    <t>£16.96</t>
-  </si>
-  <si>
-    <t>£21.12</t>
-  </si>
-  <si>
-    <t>£23.8</t>
-  </si>
-  <si>
-    <t>£23.05</t>
-  </si>
-  <si>
-    <t>£26.23</t>
-  </si>
-  <si>
-    <t>£28.99</t>
-  </si>
-  <si>
-    <t>£35.09</t>
-  </si>
-  <si>
-    <t>£36.27</t>
-  </si>
-  <si>
-    <t>£41.12</t>
-  </si>
-  <si>
-    <t>£44.39</t>
-  </si>
-  <si>
-    <t>£43.55</t>
-  </si>
-  <si>
-    <t>£697.98</t>
-  </si>
-  <si>
-    <t>£939.1</t>
-  </si>
-  <si>
-    <t>£40.65</t>
-  </si>
-  <si>
-    <t>£48.65</t>
-  </si>
-  <si>
-    <t>£57.54</t>
-  </si>
-  <si>
-    <t>£61.03</t>
-  </si>
-  <si>
-    <t>£45.36</t>
-  </si>
-  <si>
-    <t>£43.3</t>
-  </si>
-  <si>
-    <t>£44.58</t>
-  </si>
-  <si>
-    <t>£1163.76</t>
-  </si>
-  <si>
-    <t>£1238.58</t>
-  </si>
-  <si>
-    <t>£1206.21</t>
-  </si>
-  <si>
-    <t>Price Not Found</t>
-  </si>
-  <si>
-    <t>£11.28</t>
-  </si>
-  <si>
-    <t>£13.05</t>
-  </si>
-  <si>
-    <t>£16.05</t>
-  </si>
-  <si>
-    <t>£17.83</t>
-  </si>
-  <si>
-    <t>£21.36</t>
-  </si>
-  <si>
-    <t>£23.13</t>
-  </si>
-  <si>
-    <t>£23.53</t>
-  </si>
-  <si>
-    <t>£25.89</t>
-  </si>
-  <si>
-    <t>£33.90</t>
-  </si>
-  <si>
-    <t>£29.72</t>
-  </si>
-  <si>
-    <t>£56.06</t>
-  </si>
-  <si>
-    <t>£35.79</t>
-  </si>
-  <si>
-    <t>£40.85</t>
-  </si>
-  <si>
-    <t>£44.28</t>
-  </si>
-  <si>
-    <t>£43.42</t>
-  </si>
-  <si>
-    <t>£1055.68</t>
-  </si>
-  <si>
-    <t>£1280.46</t>
-  </si>
-  <si>
-    <t>£53.06</t>
-  </si>
-  <si>
-    <t>£64.38</t>
-  </si>
-  <si>
-    <t>£72.69</t>
-  </si>
-  <si>
-    <t>£75.76</t>
-  </si>
-  <si>
-    <t>£72.03</t>
-  </si>
-  <si>
-    <t>£69.95</t>
-  </si>
-  <si>
-    <t>£1582.88</t>
-  </si>
-  <si>
-    <t>£68.22</t>
-  </si>
-  <si>
-    <t>£1747.68</t>
-  </si>
-  <si>
-    <t>£1870.08</t>
-  </si>
-  <si>
-    <t>£1984.64</t>
-  </si>
-  <si>
-    <t>£23.87</t>
-  </si>
-  <si>
-    <t>£29.74</t>
-  </si>
-  <si>
-    <t>£32.42</t>
-  </si>
-  <si>
-    <t>£46.64</t>
-  </si>
-  <si>
-    <t>£46.55</t>
-  </si>
-  <si>
-    <t>£51.70</t>
-  </si>
-  <si>
-    <t>£57.31</t>
-  </si>
-  <si>
-    <t>£49.55</t>
-  </si>
-  <si>
-    <t>£74.18</t>
-  </si>
-  <si>
-    <t>£81.55</t>
-  </si>
-  <si>
-    <t>£86.21</t>
-  </si>
-  <si>
-    <t>£89.87</t>
-  </si>
-  <si>
-    <t>£51.20</t>
-  </si>
-  <si>
-    <t>£59.20</t>
-  </si>
-  <si>
-    <t>£79.58</t>
-  </si>
-  <si>
-    <t>£70.18</t>
-  </si>
-  <si>
-    <t>£12.07</t>
-  </si>
-  <si>
-    <t>£15.24</t>
-  </si>
-  <si>
-    <t>£19.67</t>
-  </si>
-  <si>
-    <t>£22.05</t>
-  </si>
-  <si>
-    <t>£22.09</t>
-  </si>
-  <si>
-    <t>£25.07</t>
-  </si>
-  <si>
-    <t>£27.59</t>
-  </si>
-  <si>
-    <t>£27.15</t>
-  </si>
-  <si>
-    <t>£32.99</t>
-  </si>
-  <si>
-    <t>£33.38</t>
-  </si>
-  <si>
-    <t>£39.79</t>
-  </si>
-  <si>
-    <t>£41.99</t>
-  </si>
-  <si>
-    <t>£779.88</t>
-  </si>
-  <si>
-    <t>£1019.88</t>
-  </si>
-  <si>
-    <t>£28.12</t>
-  </si>
-  <si>
-    <t>£34.75</t>
-  </si>
-  <si>
-    <t>£42.40</t>
-  </si>
-  <si>
-    <t>£45.74</t>
-  </si>
-  <si>
-    <t>£43.75</t>
-  </si>
-  <si>
-    <t>£924.00</t>
-  </si>
-  <si>
-    <t>£43.69</t>
-  </si>
-  <si>
-    <t>£1199.84</t>
-  </si>
-  <si>
-    <t>£1336.0</t>
-  </si>
-  <si>
-    <t>£1359.84</t>
-  </si>
-  <si>
-    <t>£10.3</t>
-  </si>
-  <si>
-    <t>£12.09</t>
-  </si>
-  <si>
-    <t>£15.86</t>
-  </si>
-  <si>
-    <t>£22.0</t>
-  </si>
-  <si>
-    <t>£27.4</t>
-  </si>
-  <si>
-    <t>£26.8</t>
-  </si>
-  <si>
-    <t>£32.98</t>
-  </si>
-  <si>
-    <t>£39.4</t>
-  </si>
-  <si>
-    <t>£804.0</t>
-  </si>
-  <si>
-    <t>£945.0</t>
-  </si>
-  <si>
-    <t>£28.03</t>
-  </si>
-  <si>
-    <t>£37.07</t>
-  </si>
-  <si>
-    <t>£42.15</t>
-  </si>
-  <si>
-    <t>£55.13</t>
-  </si>
-  <si>
-    <t>£53.4</t>
-  </si>
-  <si>
-    <t>£51.65</t>
-  </si>
-  <si>
-    <t>£1248.0</t>
-  </si>
-  <si>
-    <t>£1328.0</t>
-  </si>
-  <si>
-    <t>£1280.0</t>
-  </si>
-  <si>
-    <t>£10.15</t>
-  </si>
-  <si>
-    <t>£12.55</t>
-  </si>
-  <si>
-    <t>£14.83</t>
-  </si>
-  <si>
-    <t>£15.77</t>
-  </si>
-  <si>
-    <t>£19.71</t>
-  </si>
-  <si>
-    <t>£22.11</t>
-  </si>
-  <si>
-    <t>£25.12</t>
-  </si>
-  <si>
-    <t>£27.44</t>
-  </si>
-  <si>
-    <t>£26.49</t>
-  </si>
-  <si>
-    <t>£38.80</t>
-  </si>
-  <si>
-    <t>£38.92</t>
-  </si>
-  <si>
-    <t>£39.81</t>
-  </si>
-  <si>
-    <t>£9008.4</t>
-  </si>
-  <si>
-    <t>Error: could not convert string to float: '1,035.75'</t>
-  </si>
-  <si>
-    <t>£28.33</t>
-  </si>
-  <si>
-    <t>£32.69</t>
-  </si>
-  <si>
-    <t>£35.92</t>
-  </si>
-  <si>
-    <t>£40.99</t>
-  </si>
-  <si>
-    <t>£44.16</t>
-  </si>
-  <si>
-    <t>£43.59</t>
-  </si>
-  <si>
-    <t>£43.14</t>
-  </si>
-  <si>
-    <t>£1224.64</t>
-  </si>
-  <si>
-    <t>£1377.12</t>
-  </si>
-  <si>
-    <t>£16.66</t>
-  </si>
-  <si>
-    <t>£17.30</t>
-  </si>
-  <si>
-    <t>£21.13</t>
-  </si>
-  <si>
-    <t>£24.35</t>
-  </si>
-  <si>
-    <t>£23.47</t>
-  </si>
-  <si>
-    <t>£26.39</t>
-  </si>
-  <si>
-    <t>£29.78</t>
   </si>
   <si>
     <t>£36.01</t>
@@ -1560,49 +1521,49 @@
         <v>74</v>
       </c>
       <c r="D2" t="s">
-        <v>74</v>
+        <v>101</v>
       </c>
       <c r="E2" t="s">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="F2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="G2" t="s">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="H2" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="I2" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="J2" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="K2" t="s">
-        <v>214</v>
+        <v>198</v>
       </c>
       <c r="L2" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="M2" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="N2" t="s">
-        <v>269</v>
+        <v>172</v>
       </c>
       <c r="O2" t="s">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="P2" t="s">
-        <v>309</v>
+        <v>294</v>
       </c>
       <c r="Q2" t="s">
-        <v>328</v>
+        <v>313</v>
       </c>
       <c r="R2" t="s">
-        <v>166</v>
+        <v>336</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1622,43 +1583,43 @@
         <v>75</v>
       </c>
       <c r="F3" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="G3" t="s">
         <v>75</v>
       </c>
       <c r="H3" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="I3" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="J3" t="s">
-        <v>191</v>
+        <v>175</v>
       </c>
       <c r="K3" t="s">
-        <v>215</v>
+        <v>199</v>
       </c>
       <c r="L3" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="M3" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="N3" t="s">
-        <v>171</v>
+        <v>253</v>
       </c>
       <c r="O3" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="P3" t="s">
-        <v>310</v>
+        <v>295</v>
       </c>
       <c r="Q3" t="s">
-        <v>329</v>
+        <v>314</v>
       </c>
       <c r="R3" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1672,49 +1633,49 @@
         <v>76</v>
       </c>
       <c r="D4" t="s">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="E4" t="s">
         <v>76</v>
       </c>
       <c r="F4" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="G4" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="H4" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="I4" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="J4" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="K4" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="L4" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="M4" t="s">
-        <v>243</v>
+        <v>227</v>
       </c>
       <c r="N4" t="s">
-        <v>270</v>
+        <v>254</v>
       </c>
       <c r="O4" t="s">
-        <v>286</v>
+        <v>271</v>
       </c>
       <c r="P4" t="s">
         <v>76</v>
       </c>
       <c r="Q4" t="s">
-        <v>330</v>
+        <v>315</v>
       </c>
       <c r="R4" t="s">
-        <v>351</v>
+        <v>337</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1728,49 +1689,49 @@
         <v>77</v>
       </c>
       <c r="D5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E5" t="s">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="F5" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G5" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="H5" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="J5" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="K5" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="L5" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="M5" t="s">
-        <v>244</v>
+        <v>228</v>
       </c>
       <c r="N5" t="s">
-        <v>271</v>
+        <v>255</v>
       </c>
       <c r="O5" t="s">
         <v>77</v>
       </c>
       <c r="P5" t="s">
-        <v>311</v>
+        <v>296</v>
       </c>
       <c r="Q5" t="s">
-        <v>331</v>
+        <v>316</v>
       </c>
       <c r="R5" t="s">
-        <v>352</v>
+        <v>338</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1790,43 +1751,43 @@
         <v>78</v>
       </c>
       <c r="F6" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="G6" t="s">
-        <v>78</v>
+        <v>131</v>
       </c>
       <c r="H6" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="I6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J6" t="s">
-        <v>194</v>
+        <v>178</v>
       </c>
       <c r="K6" t="s">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="L6" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="M6" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="N6" t="s">
-        <v>171</v>
+        <v>256</v>
       </c>
       <c r="O6" t="s">
-        <v>287</v>
+        <v>272</v>
       </c>
       <c r="P6" t="s">
         <v>78</v>
       </c>
       <c r="Q6" t="s">
-        <v>332</v>
+        <v>317</v>
       </c>
       <c r="R6" t="s">
-        <v>353</v>
+        <v>339</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1846,43 +1807,43 @@
         <v>79</v>
       </c>
       <c r="F7" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="G7" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="H7" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="I7" t="s">
         <v>171</v>
       </c>
       <c r="J7" t="s">
-        <v>195</v>
+        <v>179</v>
       </c>
       <c r="K7" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="L7" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="M7" t="s">
-        <v>246</v>
+        <v>230</v>
       </c>
       <c r="N7" t="s">
-        <v>272</v>
+        <v>257</v>
       </c>
       <c r="O7" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="P7" t="s">
-        <v>312</v>
+        <v>297</v>
       </c>
       <c r="Q7" t="s">
         <v>79</v>
       </c>
       <c r="R7" t="s">
-        <v>354</v>
+        <v>340</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1902,43 +1863,43 @@
         <v>79</v>
       </c>
       <c r="F8" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="G8" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="H8" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="I8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J8" t="s">
-        <v>196</v>
+        <v>180</v>
       </c>
       <c r="K8" t="s">
-        <v>220</v>
+        <v>204</v>
       </c>
       <c r="L8" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="M8" t="s">
-        <v>247</v>
+        <v>231</v>
       </c>
       <c r="N8" t="s">
-        <v>273</v>
+        <v>258</v>
       </c>
       <c r="O8" t="s">
-        <v>289</v>
+        <v>274</v>
       </c>
       <c r="P8" t="s">
-        <v>312</v>
+        <v>297</v>
       </c>
       <c r="Q8" t="s">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="R8" t="s">
-        <v>355</v>
+        <v>341</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1958,43 +1919,43 @@
         <v>80</v>
       </c>
       <c r="F9" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="G9" t="s">
         <v>80</v>
       </c>
       <c r="H9" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="I9" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J9" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="K9" t="s">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="L9" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="M9" t="s">
-        <v>248</v>
+        <v>232</v>
       </c>
       <c r="N9" t="s">
-        <v>274</v>
+        <v>259</v>
       </c>
       <c r="O9" t="s">
-        <v>290</v>
+        <v>275</v>
       </c>
       <c r="P9" t="s">
-        <v>290</v>
+        <v>275</v>
       </c>
       <c r="Q9" t="s">
-        <v>334</v>
+        <v>319</v>
       </c>
       <c r="R9" t="s">
-        <v>356</v>
+        <v>342</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -2014,43 +1975,43 @@
         <v>81</v>
       </c>
       <c r="F10" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="G10" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="H10" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="I10" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="J10" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="K10" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="L10" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="M10" t="s">
-        <v>249</v>
+        <v>233</v>
       </c>
       <c r="N10" t="s">
-        <v>275</v>
+        <v>260</v>
       </c>
       <c r="O10" t="s">
-        <v>291</v>
+        <v>276</v>
       </c>
       <c r="P10" t="s">
-        <v>313</v>
+        <v>298</v>
       </c>
       <c r="Q10" t="s">
-        <v>335</v>
+        <v>320</v>
       </c>
       <c r="R10" t="s">
-        <v>357</v>
+        <v>343</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -2070,43 +2031,43 @@
         <v>82</v>
       </c>
       <c r="F11" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G11" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="H11" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="I11" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="J11" t="s">
-        <v>199</v>
+        <v>183</v>
       </c>
       <c r="K11" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="L11" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="M11" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="N11" t="s">
-        <v>276</v>
+        <v>261</v>
       </c>
       <c r="O11" t="s">
-        <v>292</v>
+        <v>277</v>
       </c>
       <c r="P11" t="s">
-        <v>314</v>
+        <v>299</v>
       </c>
       <c r="Q11" t="s">
-        <v>336</v>
+        <v>321</v>
       </c>
       <c r="R11" t="s">
-        <v>174</v>
+        <v>344</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -2126,43 +2087,43 @@
         <v>83</v>
       </c>
       <c r="F12" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="G12" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="H12" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="I12" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="J12" t="s">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="K12" t="s">
-        <v>223</v>
+        <v>207</v>
       </c>
       <c r="L12" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="M12" t="s">
-        <v>251</v>
+        <v>235</v>
       </c>
       <c r="N12" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O12" t="s">
-        <v>293</v>
+        <v>278</v>
       </c>
       <c r="P12" t="s">
-        <v>271</v>
+        <v>255</v>
       </c>
       <c r="Q12" t="s">
-        <v>271</v>
+        <v>255</v>
       </c>
       <c r="R12" t="s">
-        <v>358</v>
+        <v>345</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -2182,43 +2143,43 @@
         <v>84</v>
       </c>
       <c r="F13" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="G13" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="H13" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="I13" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="J13" t="s">
-        <v>201</v>
+        <v>185</v>
       </c>
       <c r="K13" t="s">
+        <v>208</v>
+      </c>
+      <c r="L13" t="s">
         <v>224</v>
       </c>
-      <c r="L13" t="s">
-        <v>240</v>
-      </c>
       <c r="M13" t="s">
-        <v>252</v>
+        <v>236</v>
       </c>
       <c r="N13" t="s">
-        <v>277</v>
+        <v>262</v>
       </c>
       <c r="O13" t="s">
-        <v>294</v>
+        <v>279</v>
       </c>
       <c r="P13" t="s">
-        <v>315</v>
+        <v>300</v>
       </c>
       <c r="Q13" t="s">
         <v>84</v>
       </c>
       <c r="R13" t="s">
-        <v>359</v>
+        <v>346</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2238,43 +2199,43 @@
         <v>85</v>
       </c>
       <c r="F14" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G14" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="H14" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="I14" t="s">
         <v>171</v>
       </c>
       <c r="J14" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="K14" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="L14" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="M14" t="s">
-        <v>253</v>
+        <v>237</v>
       </c>
       <c r="N14" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="O14" t="s">
-        <v>295</v>
+        <v>280</v>
       </c>
       <c r="P14" t="s">
-        <v>316</v>
+        <v>301</v>
       </c>
       <c r="Q14" t="s">
-        <v>337</v>
+        <v>322</v>
       </c>
       <c r="R14" t="s">
-        <v>360</v>
+        <v>347</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2291,46 +2252,46 @@
         <v>86</v>
       </c>
       <c r="E15" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="F15" t="s">
         <v>97</v>
       </c>
       <c r="G15" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="H15" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="I15" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="J15" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="K15" t="s">
-        <v>226</v>
+        <v>210</v>
       </c>
       <c r="L15" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="M15" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="N15" t="s">
-        <v>279</v>
+        <v>264</v>
       </c>
       <c r="O15" t="s">
-        <v>296</v>
+        <v>281</v>
       </c>
       <c r="P15" t="s">
         <v>86</v>
       </c>
       <c r="Q15" t="s">
-        <v>338</v>
+        <v>323</v>
       </c>
       <c r="R15" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2350,31 +2311,31 @@
         <v>87</v>
       </c>
       <c r="F16" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G16" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H16" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="I16" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="J16" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="K16" t="s">
-        <v>227</v>
+        <v>211</v>
       </c>
       <c r="L16" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="M16" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
       <c r="N16" t="s">
-        <v>280</v>
+        <v>265</v>
       </c>
       <c r="O16" t="s">
         <v>87</v>
@@ -2383,10 +2344,10 @@
         <v>87</v>
       </c>
       <c r="Q16" t="s">
-        <v>339</v>
+        <v>324</v>
       </c>
       <c r="R16" t="s">
-        <v>361</v>
+        <v>348</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2406,43 +2367,43 @@
         <v>88</v>
       </c>
       <c r="F17" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="G17" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="H17" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="I17" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="J17" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="K17" t="s">
-        <v>228</v>
+        <v>212</v>
       </c>
       <c r="L17" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="M17" t="s">
-        <v>256</v>
+        <v>240</v>
       </c>
       <c r="N17" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O17" t="s">
-        <v>297</v>
+        <v>282</v>
       </c>
       <c r="P17" t="s">
-        <v>317</v>
+        <v>302</v>
       </c>
       <c r="Q17" t="s">
-        <v>340</v>
+        <v>325</v>
       </c>
       <c r="R17" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2462,43 +2423,43 @@
         <v>89</v>
       </c>
       <c r="F18" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G18" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="H18" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="I18" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="J18" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="K18" t="s">
-        <v>229</v>
+        <v>213</v>
       </c>
       <c r="L18" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="M18" t="s">
-        <v>257</v>
+        <v>241</v>
       </c>
       <c r="N18" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O18" t="s">
-        <v>298</v>
+        <v>283</v>
       </c>
       <c r="P18" t="s">
-        <v>318</v>
+        <v>303</v>
       </c>
       <c r="Q18" t="s">
-        <v>341</v>
+        <v>326</v>
       </c>
       <c r="R18" t="s">
-        <v>362</v>
+        <v>349</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2518,43 +2479,43 @@
         <v>90</v>
       </c>
       <c r="F19" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G19" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="H19" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="I19" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="J19" t="s">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c r="K19" t="s">
-        <v>230</v>
+        <v>214</v>
       </c>
       <c r="L19" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="M19" t="s">
-        <v>258</v>
+        <v>242</v>
       </c>
       <c r="N19" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="O19" t="s">
-        <v>299</v>
+        <v>284</v>
       </c>
       <c r="P19" t="s">
-        <v>319</v>
+        <v>304</v>
       </c>
       <c r="Q19" t="s">
-        <v>342</v>
+        <v>327</v>
       </c>
       <c r="R19" t="s">
-        <v>363</v>
+        <v>350</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2574,43 +2535,43 @@
         <v>91</v>
       </c>
       <c r="F20" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G20" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="H20" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="I20" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="J20" t="s">
-        <v>207</v>
+        <v>191</v>
       </c>
       <c r="K20" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="L20" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="M20" t="s">
-        <v>259</v>
+        <v>243</v>
       </c>
       <c r="N20" t="s">
-        <v>282</v>
+        <v>267</v>
       </c>
       <c r="O20" t="s">
-        <v>300</v>
+        <v>285</v>
       </c>
       <c r="P20" t="s">
         <v>91</v>
       </c>
       <c r="Q20" t="s">
-        <v>343</v>
+        <v>328</v>
       </c>
       <c r="R20" t="s">
-        <v>364</v>
+        <v>351</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2630,43 +2591,43 @@
         <v>92</v>
       </c>
       <c r="F21" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="G21" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="H21" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="I21" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="J21" t="s">
-        <v>208</v>
+        <v>192</v>
       </c>
       <c r="K21" t="s">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="L21" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="M21" t="s">
-        <v>260</v>
+        <v>244</v>
       </c>
       <c r="N21" t="s">
-        <v>283</v>
+        <v>268</v>
       </c>
       <c r="O21" t="s">
         <v>92</v>
       </c>
       <c r="P21" t="s">
-        <v>320</v>
+        <v>305</v>
       </c>
       <c r="Q21" t="s">
-        <v>344</v>
+        <v>329</v>
       </c>
       <c r="R21" t="s">
-        <v>365</v>
+        <v>352</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -2686,43 +2647,43 @@
         <v>93</v>
       </c>
       <c r="F22" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="G22" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="H22" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="I22" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="J22" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="K22" t="s">
-        <v>233</v>
+        <v>217</v>
       </c>
       <c r="L22" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="M22" t="s">
-        <v>261</v>
+        <v>245</v>
       </c>
       <c r="N22" t="s">
-        <v>284</v>
+        <v>269</v>
       </c>
       <c r="O22" t="s">
-        <v>301</v>
+        <v>286</v>
       </c>
       <c r="P22" t="s">
-        <v>321</v>
+        <v>306</v>
       </c>
       <c r="Q22" t="s">
-        <v>345</v>
+        <v>330</v>
       </c>
       <c r="R22" t="s">
-        <v>366</v>
+        <v>353</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -2742,43 +2703,43 @@
         <v>94</v>
       </c>
       <c r="F23" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="G23" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="H23" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="I23" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="J23" t="s">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="K23" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="L23" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="M23" t="s">
-        <v>262</v>
+        <v>246</v>
       </c>
       <c r="N23" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O23" t="s">
-        <v>302</v>
+        <v>287</v>
       </c>
       <c r="P23" t="s">
-        <v>322</v>
+        <v>307</v>
       </c>
       <c r="Q23" t="s">
-        <v>346</v>
+        <v>331</v>
       </c>
       <c r="R23" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -2798,43 +2759,43 @@
         <v>95</v>
       </c>
       <c r="F24" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="G24" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="H24" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="I24" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="J24" t="s">
-        <v>211</v>
+        <v>195</v>
       </c>
       <c r="K24" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="L24" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="M24" t="s">
-        <v>263</v>
+        <v>247</v>
       </c>
       <c r="N24" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O24" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="P24" t="s">
-        <v>323</v>
+        <v>308</v>
       </c>
       <c r="Q24" t="s">
-        <v>347</v>
+        <v>332</v>
       </c>
       <c r="R24" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
     </row>
     <row r="25" spans="1:18">
@@ -2854,43 +2815,43 @@
         <v>96</v>
       </c>
       <c r="F25" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="G25" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="H25" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="I25" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="J25" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="K25" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="L25" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="M25" t="s">
-        <v>264</v>
+        <v>248</v>
       </c>
       <c r="N25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O25" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="P25" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="Q25" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="R25" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="26" spans="1:18">
@@ -2910,43 +2871,43 @@
         <v>97</v>
       </c>
       <c r="F26" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="G26" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="H26" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="I26" t="s">
-        <v>187</v>
+        <v>171</v>
       </c>
       <c r="J26" t="s">
-        <v>213</v>
+        <v>197</v>
       </c>
       <c r="K26" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="L26" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="M26" t="s">
-        <v>265</v>
+        <v>249</v>
       </c>
       <c r="N26" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O26" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="P26" t="s">
-        <v>324</v>
+        <v>309</v>
       </c>
       <c r="Q26" t="s">
-        <v>348</v>
+        <v>333</v>
       </c>
       <c r="R26" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
     </row>
     <row r="27" spans="1:18">
@@ -2966,43 +2927,43 @@
         <v>98</v>
       </c>
       <c r="F27" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G27" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="H27" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="I27" t="s">
-        <v>188</v>
+        <v>171</v>
       </c>
       <c r="J27" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="K27" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
       <c r="L27" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="M27" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
       <c r="N27" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O27" t="s">
-        <v>306</v>
+        <v>291</v>
       </c>
       <c r="P27" t="s">
-        <v>325</v>
+        <v>310</v>
       </c>
       <c r="Q27" t="s">
-        <v>349</v>
+        <v>334</v>
       </c>
       <c r="R27" t="s">
-        <v>370</v>
+        <v>357</v>
       </c>
     </row>
     <row r="28" spans="1:18">
@@ -3022,43 +2983,43 @@
         <v>99</v>
       </c>
       <c r="F28" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G28" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="H28" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="I28" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
       <c r="J28" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="K28" t="s">
-        <v>238</v>
+        <v>222</v>
       </c>
       <c r="L28" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="M28" t="s">
-        <v>267</v>
+        <v>251</v>
       </c>
       <c r="N28" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O28" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="P28" t="s">
-        <v>326</v>
+        <v>311</v>
       </c>
       <c r="Q28" t="s">
-        <v>350</v>
+        <v>335</v>
       </c>
       <c r="R28" t="s">
-        <v>371</v>
+        <v>358</v>
       </c>
     </row>
     <row r="29" spans="1:18">
@@ -3078,43 +3039,43 @@
         <v>100</v>
       </c>
       <c r="F29" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G29" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="H29" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="I29" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J29" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="K29" t="s">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="L29" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="M29" t="s">
-        <v>268</v>
+        <v>252</v>
       </c>
       <c r="N29" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O29" t="s">
-        <v>308</v>
+        <v>293</v>
       </c>
       <c r="P29" t="s">
-        <v>327</v>
+        <v>312</v>
       </c>
       <c r="Q29" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="R29" t="s">
-        <v>372</v>
+        <v>359</v>
       </c>
     </row>
   </sheetData>
